--- a/output/GENMOD_Results.xlsx
+++ b/output/GENMOD_Results.xlsx
@@ -2857,16 +2857,16 @@
         <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
         <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
         <v>6</v>
@@ -2878,7 +2878,7 @@
         <v>6</v>
       </c>
       <c r="P3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q3" t="n">
         <v>6</v>
@@ -2996,7 +2996,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -3046,13 +3046,13 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>7</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -3064,7 +3064,7 @@
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -3076,7 +3076,7 @@
         <v>6</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -3114,22 +3114,22 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -3147,7 +3147,7 @@
         <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
         <v>3</v>
@@ -8783,7 +8783,7 @@
         <v>81</v>
       </c>
       <c r="O48" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="49">
@@ -9441,7 +9441,7 @@
         <v>105</v>
       </c>
       <c r="O62" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="63">
@@ -9770,7 +9770,7 @@
         <v>114</v>
       </c>
       <c r="O69" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="70">
@@ -15620,7 +15620,7 @@
         <v>94</v>
       </c>
       <c r="O51" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52">
@@ -16994,7 +16994,7 @@
         <v>81</v>
       </c>
       <c r="O9" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10">
@@ -17746,7 +17746,7 @@
         <v>105</v>
       </c>
       <c r="O25" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26">
@@ -19062,7 +19062,7 @@
         <v>94</v>
       </c>
       <c r="O53" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54">
@@ -20483,7 +20483,7 @@
         <v>81</v>
       </c>
       <c r="O12" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13">
@@ -20671,7 +20671,7 @@
         <v>94</v>
       </c>
       <c r="O16" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17">
@@ -21141,7 +21141,7 @@
         <v>105</v>
       </c>
       <c r="O26" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27">
@@ -21470,7 +21470,7 @@
         <v>114</v>
       </c>
       <c r="O33" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34">
@@ -22034,7 +22034,7 @@
         <v>81</v>
       </c>
       <c r="O45" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="46">
@@ -24322,7 +24322,7 @@
         <v>7</v>
       </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
         <v>0.878714285714286</v>
@@ -24398,7 +24398,7 @@
         <v>7</v>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J30" t="n">
         <v>0.878714285714286</v>
@@ -24436,7 +24436,7 @@
         <v>7</v>
       </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
         <v>0.878714285714286</v>
@@ -24588,7 +24588,7 @@
         <v>7</v>
       </c>
       <c r="I35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J35" t="n">
         <v>0.384428571428571</v>
@@ -25880,7 +25880,7 @@
         <v>7</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
         <v>0.943285714285714</v>
@@ -26412,7 +26412,7 @@
         <v>7</v>
       </c>
       <c r="I83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0.944571428571429</v>
@@ -26488,7 +26488,7 @@
         <v>7</v>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0.944857142857143</v>
@@ -26640,7 +26640,7 @@
         <v>7</v>
       </c>
       <c r="I89" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J89" t="n">
         <v>0.745428571428571</v>
@@ -26792,7 +26792,7 @@
         <v>7</v>
       </c>
       <c r="I93" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J93" t="n">
         <v>0.405142857142857</v>
@@ -27172,7 +27172,7 @@
         <v>7</v>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J103" t="n">
         <v>0.937142857142857</v>
@@ -27210,7 +27210,7 @@
         <v>7</v>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J104" t="n">
         <v>0.940857142857143</v>
@@ -27248,7 +27248,7 @@
         <v>7</v>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J105" t="n">
         <v>0.936714285714286</v>
@@ -27286,7 +27286,7 @@
         <v>7</v>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J106" t="n">
         <v>0.937142857142857</v>
@@ -27362,7 +27362,7 @@
         <v>7</v>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J108" t="n">
         <v>0.941285714285714</v>
@@ -27590,7 +27590,7 @@
         <v>7</v>
       </c>
       <c r="I114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J114" t="n">
         <v>0.912</v>
@@ -27972,7 +27972,7 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
         <v>6</v>
@@ -28080,7 +28080,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
@@ -28121,7 +28121,7 @@
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
@@ -28258,16 +28258,16 @@
         <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
         <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -28337,7 +28337,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -28357,13 +28357,13 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>7</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -28375,7 +28375,7 @@
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -28395,22 +28395,22 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -33141,7 +33141,7 @@
         <v>105</v>
       </c>
       <c r="O29" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30">
@@ -42527,7 +42527,7 @@
         <v>81</v>
       </c>
       <c r="O15" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16">
@@ -46204,7 +46204,7 @@
         <v>94</v>
       </c>
       <c r="O22" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23">
